--- a/public/sap-reporting/expansion-150-downloads/EXT-MM28-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-MM28-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rde2b9c1ad1b546de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R58aa1d7a5c5a41dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R0a6d94e1b1e14dc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Reb065d61638f4690"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R6d22ba09b36e4526"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R8b9e0e35d6cb47bb"/>
   </x:sheets>
 </x:workbook>
 </file>
